--- a/forms/trg/Formulir_TRG_termite.xlsx
+++ b/forms/trg/Formulir_TRG_termite.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B31)</f>
+        <f>COUNTA(Anggota!B5:B32)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F31)</f>
+        <f>COUNTA(Anggota!F5:F32)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,18 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Andi Gita Maulidyah, S.Si., M.Si.</t>
+          <t>Prof. Dr. Ir. Astuti Arif, S.Hut., M.Si., IPU</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Instansi xxxxx</t>
+          <t>Wood Chemical and Biodeterioration; Hasanuddin Uiversity</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -933,7 +933,11 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57194242248</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -946,39 +950,27 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Sitti Nuraeni, M.P</t>
+          <t>Dr. Andi Gita Maulidyah, S.Si., M.Si.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n"/>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Forest Entomologi</t>
+          <t>Instansi xxxxx</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-0095-7967</t>
-        </is>
-      </c>
+      <c r="J6" s="12" t="n"/>
       <c r="K6" s="12" t="n"/>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>57209641766</t>
-        </is>
-      </c>
+      <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -991,27 +983,39 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>dr. Isra Wahid, Ph.D.</t>
+          <t>Dr. Ir. Sitti Nuraeni, M.P</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="n"/>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Instansi xxxxx</t>
+          <t>Forest Entomologi</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-0095-7967</t>
+        </is>
+      </c>
       <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>57209641766</t>
+        </is>
+      </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1024,39 +1028,27 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Syahribulan, S.Si., M.Si.</t>
+          <t>dr. Isra Wahid, Ph.D.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>Universitas Hasanuddin</t>
-        </is>
-      </c>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Taksonomi dan Ekologi Serangga</t>
+          <t>Instansi xxxxx</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>0000-0003-0246-5699</t>
-        </is>
-      </c>
+      <c r="J8" s="12" t="n"/>
       <c r="K8" s="12" t="n"/>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>57215688204</t>
-        </is>
-      </c>
+      <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1069,27 +1061,39 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ambeng, M.Si.</t>
+          <t>Dr. Syahribulan, S.Si., M.Si.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n"/>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Universitas Hasanuddin</t>
+        </is>
+      </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Instansi xxxxx</t>
+          <t>Taksonomi dan Ekologi Serangga</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-0246-5699</t>
+        </is>
+      </c>
       <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>57215688204</t>
+        </is>
+      </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1102,22 +1106,18 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Thomas Wood</t>
+          <t>Prof. Dr. Ambeng, M.Si.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>Naturalis Biodiversity Center (NBC), Leiden</t>
-        </is>
-      </c>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n"/>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Soliter Honey Bee</t>
+          <t>Instansi xxxxx</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1139,18 +1139,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Rosichon Ubaidillah, M.Phil., Ph.D.</t>
+          <t>Dr. Thomas Wood</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Naturalis Biodiversity Center (NBC), Leiden</t>
+        </is>
+      </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>PRBE-BRIN</t>
+          <t>Soliter Honey Bee</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1159,11 +1163,7 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>6507239738</t>
-        </is>
-      </c>
+      <c r="L11" s="12" t="n"/>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1176,22 +1176,18 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dr. Veera Singham a/I K. Genasan</t>
+          <t>Prof. Rosichon Ubaidillah, M.Phil., Ph.D.</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>Universiti Sains Malaysia</t>
-        </is>
-      </c>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n"/>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Entomology , Molecular Genetics, Phylogenetics ,Population Genetics</t>
+          <t>PRBE-BRIN</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1200,7 +1196,11 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>6507239738</t>
+        </is>
+      </c>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1213,22 +1213,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr. Thomas von Rintelen</t>
+          <t>Dr. Veera Singham a/I K. Genasan</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Museum für Naturkunde</t>
+          <t>Universiti Sains Malaysia</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Malacologist</t>
+          <t>Entomology , Molecular Genetics, Phylogenetics ,Population Genetics</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1250,18 +1250,22 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Suleman Yusuf, M.Agr</t>
+          <t>Dr. Thomas von Rintelen</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Museum für Naturkunde</t>
+        </is>
+      </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>PRZT-BRIN</t>
+          <t>Malacologist</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1283,18 +1287,18 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Rustam, M.Hum</t>
+          <t>Prof. Dr. Suleman Yusuf, M.Agr</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Indonesian Heritage Agency</t>
+          <t>PRZT-BRIN</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1316,22 +1320,18 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Giselawati Putri, S.Hut., M.Hut</t>
+          <t>Rustam, M.Hum</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>Instansi xxxxx</t>
-        </is>
-      </c>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="n"/>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Forestry &amp; Environment Laboratorium</t>
+          <t>Indonesian Heritage Agency</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1353,22 +1353,22 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Ahmad Fauzan</t>
+          <t>Giselawati Putri, S.Hut., M.Hut</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Instansi xxxxx</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Graduate</t>
+          <t>Forestry &amp; Environment Laboratorium</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Nur Muhammad Mu’adz Mustafa</t>
+          <t>Ahmad Fauzan</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Instansi xxxxx</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>(Doctoral/Magister/GRaduate)</t>
+          <t>Graduate</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
@@ -1427,22 +1427,22 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Riska Febrianti</t>
+          <t>Nur Muhammad Mu’adz Mustafa</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Graduate</t>
+          <t>Instansi xxxxx</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Termite-RG</t>
+          <t>(Doctoral/Magister/GRaduate)</t>
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
@@ -1462,10 +1462,26 @@
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="11" t="n"/>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Riska Febrianti</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Graduate</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Termite-RG</t>
+        </is>
+      </c>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="n"/>
@@ -1473,7 +1489,11 @@
       <c r="J20" s="12" t="n"/>
       <c r="K20" s="12" t="n"/>
       <c r="L20" s="12" t="n"/>
-      <c r="M20" s="12" t="n"/>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1662,15 +1682,32 @@
       <c r="L31" s="12" t="n"/>
       <c r="M31" s="12" t="n"/>
     </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
